--- a/templates/在庫台帳.xlsx
+++ b/templates/在庫台帳.xlsx
@@ -7,16 +7,6 @@
 </workbook>
 </file>
 
-<file path=xl/joPython.xml><?xml version="1.0" encoding="utf-8"?>
-<joPython>
-  <script name="関数">def 要発注(r):
-    out = [[row[0], row[2], row[3]] for row in r
-           if row[0] and row[2] is not None and row[3] is not None and row[2] &lt; row[3]]
-    return out or [["(無し)", "", ""]]
-</script>
-</joPython>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
@@ -61,8 +51,63 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><fonts count="2"><font></font><font><b/></font></fonts><fills count="3"><fill><patternFill patternType="none"/></fill><fill><patternFill patternType="gray125"/></fill><fill><patternFill patternType="solid"><fgColor rgb="FFD5E8DC"/><bgColor indexed="64"/></patternFill></fill></fills><borders count="2"><border><left/><right/><top/><bottom/><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border></borders><cellStyleXfs count="1"><xf numFmtId="0" fontId="0" fillId="0" borderId="0"/></cellStyleXfs><cellXfs count="2"><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/></cellXfs><cellStyles count="1"><cellStyle name="標準" xfId="0" builtinId="0"/></cellStyles></styleSheet>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5E8DC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -119,8 +164,8 @@
         <v>1500000</v>
       </c>
       <c r="H2" t="e">
-        <f>PY("要発注", A2:D100)</f>
-        <v>#PY?</v>
+        <f>要発注(A2:D100)</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="3">
